--- a/corr_matrix/residual_exam2A_1PL.xlsx
+++ b/corr_matrix/residual_exam2A_1PL.xlsx
@@ -429,6 +429,11 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>question_id</t>
+        </is>
+      </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
           <t>2A01</t>
@@ -520,49 +525,49 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.1748058081783767</v>
+        <v>-0.1747931809907534</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.2538739042109657</v>
+        <v>-0.2538866310477798</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.1167673086810223</v>
+        <v>-0.1167711109698927</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.1930705590820001</v>
+        <v>-0.1930512329768003</v>
       </c>
       <c r="G2" t="n">
-        <v>0.07997362132109299</v>
+        <v>0.07999052873282389</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.1196090655191361</v>
+        <v>-0.1195914475695173</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1395576220257343</v>
+        <v>-0.1395744106035296</v>
       </c>
       <c r="J2" t="n">
-        <v>0.05920292064879142</v>
+        <v>0.05922010878480218</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.09167758960076552</v>
+        <v>-0.09166996668941794</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.1113617007849404</v>
+        <v>-0.1113554108008459</v>
       </c>
       <c r="M2" t="n">
-        <v>0.01382730556590064</v>
+        <v>0.01382409880550934</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.09147814289343977</v>
+        <v>-0.091492510081225</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.2338267362920154</v>
+        <v>-0.2338316996563397</v>
       </c>
       <c r="P2" t="n">
-        <v>0.006291475533940181</v>
+        <v>0.006309061414902016</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.2420422501549197</v>
+        <v>-0.2420367469665321</v>
       </c>
     </row>
     <row r="3">
@@ -572,52 +577,52 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.1748058081783767</v>
+        <v>-0.1747931809907534</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.3711463206920719</v>
+        <v>0.3711327380860997</v>
       </c>
       <c r="E3" t="n">
-        <v>0.08595161525079253</v>
+        <v>0.08592047619484698</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.07367843889074399</v>
+        <v>-0.07369436762130703</v>
       </c>
       <c r="G3" t="n">
-        <v>0.001017426128400545</v>
+        <v>0.001031352291174714</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.2858109371448422</v>
+        <v>-0.2857966613237797</v>
       </c>
       <c r="I3" t="n">
-        <v>0.09623488033776265</v>
+        <v>0.09622849519074775</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.1628535267279098</v>
+        <v>-0.1628545703587846</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.08885131894501232</v>
+        <v>-0.08886469407519344</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.06155590235366647</v>
+        <v>-0.0615933200345385</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.1691189430876193</v>
+        <v>-0.1691230250711557</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.004559003063055818</v>
+        <v>-0.004596462866082698</v>
       </c>
       <c r="O3" t="n">
-        <v>0.02290479294922772</v>
+        <v>0.02287811594309896</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.06897716791111931</v>
+        <v>-0.06897711750023228</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.05050738030530263</v>
+        <v>-0.05050779745661524</v>
       </c>
     </row>
     <row r="4">
@@ -627,52 +632,52 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.2538739042109657</v>
+        <v>-0.2538866310477798</v>
       </c>
       <c r="C4" t="n">
-        <v>0.3711463206920719</v>
+        <v>0.3711327380860997</v>
       </c>
       <c r="D4" t="n">
         <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>0.06152851123431762</v>
+        <v>0.06152553660026746</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.1182873035482175</v>
+        <v>-0.11831069099454</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.1981563557675232</v>
+        <v>-0.1981745333133217</v>
       </c>
       <c r="H4" t="n">
-        <v>0.004326510146213199</v>
+        <v>0.004322780245957547</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2197438754527168</v>
+        <v>0.2197539406999071</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.03975240486114827</v>
+        <v>-0.03976304513246573</v>
       </c>
       <c r="K4" t="n">
-        <v>0.07304904417624562</v>
+        <v>0.07303996712902941</v>
       </c>
       <c r="L4" t="n">
-        <v>0.04297521061778038</v>
+        <v>0.04296167751517978</v>
       </c>
       <c r="M4" t="n">
-        <v>0.03697079498064727</v>
+        <v>0.03695011942881388</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.048633551079932</v>
+        <v>-0.04862875989105272</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.09684057310269514</v>
+        <v>-0.09684579839445842</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.2682287800321931</v>
+        <v>-0.2682413020141975</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.1375832642480051</v>
+        <v>-0.1375720646062565</v>
       </c>
     </row>
     <row r="5">
@@ -682,52 +687,52 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.1167673086810223</v>
+        <v>-0.1167711109698927</v>
       </c>
       <c r="C5" t="n">
-        <v>0.08595161525079253</v>
+        <v>0.08592047619484698</v>
       </c>
       <c r="D5" t="n">
-        <v>0.06152851123431762</v>
+        <v>0.06152553660026746</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0957692461386724</v>
+        <v>0.09574706966751287</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.04809182492269062</v>
+        <v>-0.04809500870317474</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.2301286758072801</v>
+        <v>-0.2301277832260946</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01345217511833767</v>
+        <v>0.01346633635808226</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.2195676169013309</v>
+        <v>-0.219584720737678</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.02935465931091134</v>
+        <v>-0.02936771014574579</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0008759017992557598</v>
+        <v>0.000844470530403931</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.1494192583775889</v>
+        <v>-0.1494185716687227</v>
       </c>
       <c r="N5" t="n">
-        <v>0.07359261362828112</v>
+        <v>0.07357515200852988</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1034414996499903</v>
+        <v>0.1034273888532093</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0973752007327137</v>
+        <v>0.09736226426496034</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.3026481119229847</v>
+        <v>-0.3026665846687025</v>
       </c>
     </row>
     <row r="6">
@@ -737,52 +742,52 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.1930705590820001</v>
+        <v>-0.1930512329768003</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.07367843889074399</v>
+        <v>-0.07369436762130703</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1182873035482175</v>
+        <v>-0.11831069099454</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0957692461386724</v>
+        <v>0.09574706966751287</v>
       </c>
       <c r="F6" t="n">
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.1557350104753877</v>
+        <v>-0.1557053602852673</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.0673626217969313</v>
+        <v>-0.06734233062867631</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2676702748715934</v>
+        <v>-0.2676770042947892</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.2398579766329301</v>
+        <v>-0.2398445606503223</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.1660037636579081</v>
+        <v>-0.166003538145455</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2036876289414913</v>
+        <v>0.2036698223740536</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.1213387412283116</v>
+        <v>-0.1213337132430636</v>
       </c>
       <c r="N6" t="n">
-        <v>0.022175342252304</v>
+        <v>0.02213986864703698</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0420332139621785</v>
+        <v>0.04201405799406403</v>
       </c>
       <c r="P6" t="n">
-        <v>0.1919682745244431</v>
+        <v>0.1919805368037125</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.08355835044874305</v>
+        <v>-0.08355197195631089</v>
       </c>
     </row>
     <row r="7">
@@ -792,52 +797,52 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.07997362132109299</v>
+        <v>0.07999052873282389</v>
       </c>
       <c r="C7" t="n">
-        <v>0.001017426128400545</v>
+        <v>0.001031352291174714</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.1981563557675232</v>
+        <v>-0.1981745333133217</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.04809182492269062</v>
+        <v>-0.04809500870317474</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.1557350104753877</v>
+        <v>-0.1557053602852673</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.06086058440432451</v>
+        <v>-0.06084062623602404</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1274593202221857</v>
+        <v>-0.1274715764867716</v>
       </c>
       <c r="J7" t="n">
-        <v>0.02047371787569682</v>
+        <v>0.02049580934699981</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.1147556681381735</v>
+        <v>-0.1147379531941194</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.138518120482918</v>
+        <v>-0.1385127003728764</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.101255822978736</v>
+        <v>-0.1012391715090937</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.2202103393686179</v>
+        <v>-0.2202309621208722</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.3920907192113089</v>
+        <v>-0.392089201311388</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.002422562024243043</v>
+        <v>-0.002393949011876813</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.1086913245258349</v>
+        <v>-0.1086831967704414</v>
       </c>
     </row>
     <row r="8">
@@ -847,52 +852,52 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.1196090655191361</v>
+        <v>-0.1195914475695173</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.2858109371448422</v>
+        <v>-0.2857966613237797</v>
       </c>
       <c r="D8" t="n">
-        <v>0.004326510146213199</v>
+        <v>0.004322780245957547</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.2301286758072801</v>
+        <v>-0.2301277832260946</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.0673626217969313</v>
+        <v>-0.06734233062867631</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.06086058440432451</v>
+        <v>-0.06084062623602404</v>
       </c>
       <c r="H8" t="n">
         <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1596163390893176</v>
+        <v>0.1596014535603107</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.164164447661795</v>
+        <v>-0.1641485679598927</v>
       </c>
       <c r="K8" t="n">
-        <v>0.04253885223338429</v>
+        <v>0.04254682251500849</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.03352054061075345</v>
+        <v>-0.03350825110555934</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1083761759847539</v>
+        <v>0.1083813620046669</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.08930197348720423</v>
+        <v>-0.08930615058592106</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.05080799795854417</v>
+        <v>-0.05080705263265437</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.3548261392594101</v>
+        <v>-0.3548049827341591</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.0692370434451469</v>
+        <v>-0.06923837267641862</v>
       </c>
     </row>
     <row r="9">
@@ -902,52 +907,52 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.1395576220257343</v>
+        <v>-0.1395744106035296</v>
       </c>
       <c r="C9" t="n">
-        <v>0.09623488033776265</v>
+        <v>0.09622849519074775</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2197438754527168</v>
+        <v>0.2197539406999071</v>
       </c>
       <c r="E9" t="n">
-        <v>0.01345217511833767</v>
+        <v>0.01346633635808226</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.2676702748715934</v>
+        <v>-0.2676770042947892</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.1274593202221857</v>
+        <v>-0.1274715764867716</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1596163390893176</v>
+        <v>0.1596014535603107</v>
       </c>
       <c r="I9" t="n">
         <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.146056308224173</v>
+        <v>-0.146070493402755</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.1261171532063886</v>
+        <v>-0.1261120401267968</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.1566235301857601</v>
+        <v>-0.1566215834008679</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.09841336525514573</v>
+        <v>-0.09840252852633491</v>
       </c>
       <c r="N9" t="n">
-        <v>0.1623411502707698</v>
+        <v>0.1623616190410457</v>
       </c>
       <c r="O9" t="n">
-        <v>0.06837535943550532</v>
+        <v>0.06839082701903035</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.1872213133162243</v>
+        <v>-0.1872303412324027</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.03530253255696866</v>
+        <v>-0.03530682764028726</v>
       </c>
     </row>
     <row r="10">
@@ -957,52 +962,52 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.05920292064879142</v>
+        <v>0.05922010878480218</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.1628535267279098</v>
+        <v>-0.1628545703587846</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.03975240486114827</v>
+        <v>-0.03976304513246573</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.2195676169013309</v>
+        <v>-0.219584720737678</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2398579766329301</v>
+        <v>-0.2398445606503223</v>
       </c>
       <c r="G10" t="n">
-        <v>0.02047371787569682</v>
+        <v>0.02049580934699981</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.164164447661795</v>
+        <v>-0.1641485679598927</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.146056308224173</v>
+        <v>-0.146070493402755</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>0.04926941499308072</v>
+        <v>0.04926698259132037</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.207477129650475</v>
+        <v>-0.2074857484803624</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.1461675402593681</v>
+        <v>-0.1461597994917725</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.1206817952975887</v>
+        <v>-0.1207056221842301</v>
       </c>
       <c r="O10" t="n">
-        <v>0.07549940794396788</v>
+        <v>0.07548548025248748</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.0213452327665092</v>
+        <v>-0.02133246505570304</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.07448340292129227</v>
+        <v>-0.07449182777131803</v>
       </c>
     </row>
     <row r="11">
@@ -1012,52 +1017,52 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.09167758960076552</v>
+        <v>-0.09166996668941794</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.08885131894501232</v>
+        <v>-0.08886469407519344</v>
       </c>
       <c r="D11" t="n">
-        <v>0.07304904417624562</v>
+        <v>0.07303996712902941</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.02935465931091134</v>
+        <v>-0.02936771014574579</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.1660037636579081</v>
+        <v>-0.166003538145455</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.1147556681381735</v>
+        <v>-0.1147379531941194</v>
       </c>
       <c r="H11" t="n">
-        <v>0.04253885223338429</v>
+        <v>0.04254682251500849</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1261171532063886</v>
+        <v>-0.1261120401267968</v>
       </c>
       <c r="J11" t="n">
-        <v>0.04926941499308072</v>
+        <v>0.04926698259132037</v>
       </c>
       <c r="K11" t="n">
         <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.1561029867088616</v>
+        <v>-0.1561194962763641</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.1146554158441722</v>
+        <v>-0.1146375953664882</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.2594592597641699</v>
+        <v>-0.2594780777520886</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.2066844834065924</v>
+        <v>-0.2066925178082253</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.01304875044498608</v>
+        <v>-0.01304560293068495</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.0522598360597658</v>
+        <v>0.05225086969200152</v>
       </c>
     </row>
     <row r="12">
@@ -1067,52 +1072,52 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.1113617007849404</v>
+        <v>-0.1113554108008459</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.06155590235366647</v>
+        <v>-0.0615933200345385</v>
       </c>
       <c r="D12" t="n">
-        <v>0.04297521061778038</v>
+        <v>0.04296167751517978</v>
       </c>
       <c r="E12" t="n">
-        <v>0.0008759017992557598</v>
+        <v>0.000844470530403931</v>
       </c>
       <c r="F12" t="n">
-        <v>0.2036876289414913</v>
+        <v>0.2036698223740536</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.138518120482918</v>
+        <v>-0.1385127003728764</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.03352054061075345</v>
+        <v>-0.03350825110555934</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.1566235301857601</v>
+        <v>-0.1566215834008679</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.207477129650475</v>
+        <v>-0.2074857484803624</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.1561029867088616</v>
+        <v>-0.1561194962763641</v>
       </c>
       <c r="L12" t="n">
         <v>1</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.009962327436638945</v>
+        <v>-0.009966101753227355</v>
       </c>
       <c r="N12" t="n">
-        <v>0.0477410134482618</v>
+        <v>0.04771059615827055</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.07342942061659177</v>
+        <v>-0.07345581409273134</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.1180576819656977</v>
+        <v>-0.1180649372292883</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.0500997690269569</v>
+        <v>0.05010066308236806</v>
       </c>
     </row>
     <row r="13">
@@ -1122,52 +1127,52 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.01382730556590064</v>
+        <v>0.01382409880550934</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.1691189430876193</v>
+        <v>-0.1691230250711557</v>
       </c>
       <c r="D13" t="n">
-        <v>0.03697079498064727</v>
+        <v>0.03695011942881388</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.1494192583775889</v>
+        <v>-0.1494185716687227</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.1213387412283116</v>
+        <v>-0.1213337132430636</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.101255822978736</v>
+        <v>-0.1012391715090937</v>
       </c>
       <c r="H13" t="n">
-        <v>0.1083761759847539</v>
+        <v>0.1083813620046669</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.09841336525514573</v>
+        <v>-0.09840252852633491</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.1461675402593681</v>
+        <v>-0.1461597994917725</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.1146554158441722</v>
+        <v>-0.1146375953664882</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.009962327436638945</v>
+        <v>-0.009966101753227355</v>
       </c>
       <c r="M13" t="n">
         <v>1</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.04093679458981517</v>
+        <v>-0.04095034680795737</v>
       </c>
       <c r="O13" t="n">
-        <v>0.05509055324889623</v>
+        <v>0.05509295721231749</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.2690936191679607</v>
+        <v>-0.2690783176125603</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.1358457658697599</v>
+        <v>0.135861382270713</v>
       </c>
     </row>
     <row r="14">
@@ -1177,52 +1182,52 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.09147814289343977</v>
+        <v>-0.091492510081225</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.004559003063055818</v>
+        <v>-0.004596462866082698</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.048633551079932</v>
+        <v>-0.04862875989105272</v>
       </c>
       <c r="E14" t="n">
-        <v>0.07359261362828112</v>
+        <v>0.07357515200852988</v>
       </c>
       <c r="F14" t="n">
-        <v>0.022175342252304</v>
+        <v>0.02213986864703698</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.2202103393686179</v>
+        <v>-0.2202309621208722</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.08930197348720423</v>
+        <v>-0.08930615058592106</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1623411502707698</v>
+        <v>0.1623616190410457</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.1206817952975887</v>
+        <v>-0.1207056221842301</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.2594592597641699</v>
+        <v>-0.2594780777520886</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0477410134482618</v>
+        <v>0.04771059615827055</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.04093679458981517</v>
+        <v>-0.04095034680795737</v>
       </c>
       <c r="N14" t="n">
         <v>1</v>
       </c>
       <c r="O14" t="n">
-        <v>0.1481315115408972</v>
+        <v>0.1481187445359934</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.04297771234755112</v>
+        <v>-0.04300281429013989</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.01654462085197221</v>
+        <v>0.01653927799662085</v>
       </c>
     </row>
     <row r="15">
@@ -1232,52 +1237,52 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-0.2338267362920154</v>
+        <v>-0.2338316996563397</v>
       </c>
       <c r="C15" t="n">
-        <v>0.02290479294922772</v>
+        <v>0.02287811594309896</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.09684057310269514</v>
+        <v>-0.09684579839445842</v>
       </c>
       <c r="E15" t="n">
-        <v>0.1034414996499903</v>
+        <v>0.1034273888532093</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0420332139621785</v>
+        <v>0.04201405799406403</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.3920907192113089</v>
+        <v>-0.392089201311388</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.05080799795854417</v>
+        <v>-0.05080705263265437</v>
       </c>
       <c r="I15" t="n">
-        <v>0.06837535943550532</v>
+        <v>0.06839082701903035</v>
       </c>
       <c r="J15" t="n">
-        <v>0.07549940794396788</v>
+        <v>0.07548548025248748</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.2066844834065924</v>
+        <v>-0.2066925178082253</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.07342942061659177</v>
+        <v>-0.07345581409273134</v>
       </c>
       <c r="M15" t="n">
-        <v>0.05509055324889623</v>
+        <v>0.05509295721231749</v>
       </c>
       <c r="N15" t="n">
-        <v>0.1481315115408972</v>
+        <v>0.1481187445359934</v>
       </c>
       <c r="O15" t="n">
         <v>1</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.05011944884634555</v>
+        <v>-0.05013024101502195</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.04319239509044191</v>
+        <v>0.04318647753028737</v>
       </c>
     </row>
     <row r="16">
@@ -1287,52 +1292,52 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.006291475533940181</v>
+        <v>0.006309061414902016</v>
       </c>
       <c r="C16" t="n">
-        <v>-0.06897716791111931</v>
+        <v>-0.06897711750023228</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.2682287800321931</v>
+        <v>-0.2682413020141975</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0973752007327137</v>
+        <v>0.09736226426496034</v>
       </c>
       <c r="F16" t="n">
-        <v>0.1919682745244431</v>
+        <v>0.1919805368037125</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.002422562024243043</v>
+        <v>-0.002393949011876813</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.3548261392594101</v>
+        <v>-0.3548049827341591</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.1872213133162243</v>
+        <v>-0.1872303412324027</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.0213452327665092</v>
+        <v>-0.02133246505570304</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.01304875044498608</v>
+        <v>-0.01304560293068495</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.1180576819656977</v>
+        <v>-0.1180649372292883</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.2690936191679607</v>
+        <v>-0.2690783176125603</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.04297771234755112</v>
+        <v>-0.04300281429013989</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.05011944884634555</v>
+        <v>-0.05013024101502195</v>
       </c>
       <c r="P16" t="n">
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.1564020612943026</v>
+        <v>-0.15640471302582</v>
       </c>
     </row>
     <row r="17">
@@ -1342,49 +1347,49 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-0.2420422501549197</v>
+        <v>-0.2420367469665321</v>
       </c>
       <c r="C17" t="n">
-        <v>-0.05050738030530263</v>
+        <v>-0.05050779745661524</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1375832642480051</v>
+        <v>-0.1375720646062565</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.3026481119229847</v>
+        <v>-0.3026665846687025</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.08355835044874305</v>
+        <v>-0.08355197195631089</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.1086913245258349</v>
+        <v>-0.1086831967704414</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.0692370434451469</v>
+        <v>-0.06923837267641862</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.03530253255696866</v>
+        <v>-0.03530682764028726</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.07448340292129227</v>
+        <v>-0.07449182777131803</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0522598360597658</v>
+        <v>0.05225086969200152</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0500997690269569</v>
+        <v>0.05010066308236806</v>
       </c>
       <c r="M17" t="n">
-        <v>0.1358457658697599</v>
+        <v>0.135861382270713</v>
       </c>
       <c r="N17" t="n">
-        <v>0.01654462085197221</v>
+        <v>0.01653927799662085</v>
       </c>
       <c r="O17" t="n">
-        <v>0.04319239509044191</v>
+        <v>0.04318647753028737</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.1564020612943026</v>
+        <v>-0.15640471302582</v>
       </c>
       <c r="Q17" t="n">
         <v>1</v>
